--- a/Clase 2 - EPH e Intro a Tidyverse/Fuentes/Aglomerados y Regiones EPH.xlsx
+++ b/Clase 2 - EPH e Intro a Tidyverse/Fuentes/Aglomerados y Regiones EPH.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Guido\Trabajo\Repositorios de R\Cursos de R\Intro_R_Intensivo\Fuentes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Guido W\seminario_estadistica_desigualdad\bases_eph\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{331EA082-A29B-4821-BF43-34A08F236EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2B873B-A2C3-4CEB-AFF5-526D6554D290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="18775" windowHeight="10067" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Regiones EPH" sheetId="2" r:id="rId1"/>
-    <sheet name="Aglomerados EPH" sheetId="1" r:id="rId2"/>
+    <sheet name="Aglomerados EPH" sheetId="3" r:id="rId1"/>
+    <sheet name="Aglomerados EPH_con_titulo" sheetId="1" r:id="rId2"/>
+    <sheet name="Regiones EPH" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
   <si>
     <t>AGLOMERADO</t>
   </si>
@@ -489,64 +490,554 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F3BD2A-6948-4336-B414-94CC2A452BA7}">
-  <dimension ref="A2:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC8B0088-A91E-4770-A6C5-BD869575F5FA}">
+  <dimension ref="A1:B33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>38</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>91</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>93</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>38</v>
       </c>
-      <c r="B4">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8">
-        <v>44</v>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -555,281 +1046,65 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5" customWidth="1"/>
-  </cols>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F3BD2A-6948-4336-B414-94CC2A452BA7}">
+  <dimension ref="A2:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>17</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>19</v>
-      </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>29</v>
-      </c>
-      <c r="B28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>34</v>
-      </c>
-      <c r="B31" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>36</v>
-      </c>
-      <c r="B32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>38</v>
       </c>
-      <c r="B33" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>91</v>
-      </c>
-      <c r="B34" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>93</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
+      <c r="B4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
